--- a/config/1.逐笔统计系统_配置.xlsx
+++ b/config/1.逐笔统计系统_配置.xlsx
@@ -13,7 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务说明" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务说明" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'核查表校验结果'!$A$1:$L$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +35,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +49,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00225A9F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,9 +69,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -429,13 +447,122 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>公开表头示例：不含正式规则、机构资料、业务数据或金融表单模板。</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>配置版本</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>操作说明</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>操作步骤见《基础数据审核工具使用说明.docx》（简易版）；高级开关见《…_高级版.docx》</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>本册用途</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>逐笔统计系统专属：两个流程的审核历史与人工说明，程序只追加、不覆盖人工列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>核查表校验结果</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>汇总核查表校验的历史问题；“新增 / 连续出现 / 再次出现 / 已整改”由此判定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>本地校验结果</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>本地校验结果汇总的历史说明与状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>业务说明</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>按“来源文件、来源工作表、业务表单名称、业务表单英文名称”匹配，追加“历史说明”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>任务说明</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>按“来源文件、来源工作表、社会统一信用代码、金融机构编码、任务名称”匹配，追加“历史说明”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>人工列保护</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>“机构反馈”“审核意见”等人工填写列在程序更新时不会被覆盖，可放心维护。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>缺失或损坏</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>请到“设置中心 → 常规设置 → 逐笔统计系统配置”，点“重置结构”：只补全缺失表头，不清空已有人工记录。</t>
         </is>
       </c>
     </row>
@@ -454,68 +581,69 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>工作簿名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>工作表名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>定位单元格</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>错误类型</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>校验指标</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>当前值</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>对比值</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>差值</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>规则编号</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>历史校验说明</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>审核意见</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/config/1.逐笔统计系统_配置.xlsx
+++ b/config/1.逐笔统计系统_配置.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,42 +601,47 @@
           <t>错误类型</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>校验类型</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>校验指标</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>当前值</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>对比值</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>差值</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>规则编号</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>历史校验说明</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>审核意见</t>
         </is>
